--- a/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="CRUD 매트릭스" sheetId="1" r:id="rId1"/>
+    <sheet name="문서정보" sheetId="1" r:id="rId1"/>
+    <sheet name="CRUD 매트릭스" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -57,6 +58,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>문서명</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CRUD 매트릭스</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>방법론</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>as-built</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>소스 커밋</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[미확인]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>작성자 / 버전 / 작성일</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[미확인] — 제출 전 사람이 채움</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>본 파일의 지위</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>정적 스캔 스냅샷(원천 데이터) — 대시보드에서의 확정 편집은 반영되지 않음. 최신화는 /understand-docs 재실행.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>신뢰도 표기</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>[확정]=정적 분석 근거(file:line) 보유, [추정]=추론, [미확인]=사람 채움 대상 — 사람 검수/사인오프 여부와 무관.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B7"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
@@ -898,5 +995,6 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O23"/>
 </worksheet>
 </file>
--- a/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
@@ -844,12 +844,12 @@
       <c r="G20"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="J20"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>src/site/xdoc/index.xml:381</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:93, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:104, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:59</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="J21"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:76, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70, src/site/xdoc/index.xml:381, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:37, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:32</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:76, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:93, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:104, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:59, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:37, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:32</t>
         </is>
       </c>
     </row>
@@ -971,12 +971,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="J23"/>
@@ -990,7 +990,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>src/site/xdoc/index.xml:381, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:37, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:76, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:93, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:104, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:59, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:37, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:76, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70</t>
         </is>
       </c>
     </row>

--- a/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
@@ -306,7 +306,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -327,13 +327,13 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="L4"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>RU</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -343,7 +343,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:52, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:95, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:114, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:127, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:79, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:102, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:122, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:46</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:52, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:79, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:102, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:122, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36</t>
         </is>
       </c>
     </row>
@@ -380,7 +380,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -401,13 +401,13 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="L6"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -417,7 +417,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:52, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:95, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:114, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:127, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:79, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:102, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:122, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:46</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:52, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:95, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:114, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:127, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -500,13 +500,13 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L9"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>CRU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:52, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:95, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:114, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:127, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:79, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:102, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:122, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:46</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/AccountMapper.xml:52, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36</t>
         </is>
       </c>
     </row>
@@ -553,7 +553,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:46</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:46</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:46, src/main/resources/org/mybatis/jpetstore/mapper/CategoryMapper.xml:35, src/main/resources/org/mybatis/jpetstore/mapper/CategoryMapper.xml:26</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/CategoryMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36</t>
         </is>
       </c>
     </row>
@@ -761,11 +761,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="E18"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>R</t>
@@ -785,7 +781,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47</t>
         </is>
       </c>
     </row>
@@ -798,11 +794,7 @@
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="E19"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>R</t>
@@ -826,7 +818,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:36, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:46</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ProductMapper.xml:26</t>
         </is>
       </c>
     </row>
@@ -844,12 +836,12 @@
       <c r="G20"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J20"/>
@@ -863,7 +855,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:93, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:104, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:59</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:59</t>
         </is>
       </c>
     </row>
@@ -878,27 +870,23 @@
       <c r="D21"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RU</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F21"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J21"/>
@@ -916,7 +904,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:76, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:93, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:104, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:59, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:37, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:32</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:76, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:37, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:93, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:104, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/SequenceMapper.xml:32</t>
         </is>
       </c>
     </row>
@@ -956,7 +944,7 @@
       <c r="D23"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RU</t>
+          <t>R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -966,17 +954,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>R</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>R</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>R</t>
         </is>
       </c>
       <c r="J23"/>
@@ -990,7 +978,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:93, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:104, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:59, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:37, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:76, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70</t>
+          <t>src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:70, src/main/resources/org/mybatis/jpetstore/mapper/ItemMapper.xml:47, src/main/resources/org/mybatis/jpetstore/mapper/LineItemMapper.xml:26, src/main/resources/org/mybatis/jpetstore/mapper/OrderMapper.xml:26</t>
         </is>
       </c>
     </row>

--- a/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/07_crud-matrix.xlsx
@@ -106,7 +106,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>
